--- a/mobility-data-standard/mobility-data-standard.xlsx
+++ b/mobility-data-standard/mobility-data-standard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE1E769-95E6-4340-8DC1-C8C9037B7252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44719259-5C5E-4753-8A83-90D5A52F6C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="103">
   <si>
     <t>ConceptScheme URI</t>
   </si>
@@ -74,9 +74,6 @@
     <t>dct:publisher</t>
   </si>
   <si>
-    <t>NAPCORE SubWG4.4</t>
-  </si>
-  <si>
     <t>dct:contributor</t>
   </si>
   <si>
@@ -338,13 +335,16 @@
     <t>Dataset uses a data standard not listed in this vocabulary</t>
   </si>
   <si>
-    <t>Draft Controlled Vocabulary</t>
-  </si>
-  <si>
     <t>skos:Concept,https://w3id.org/mobilitydcatap#MobilityDataStandard</t>
   </si>
   <si>
     <t xml:space="preserve">Sara Guerra de Oliveira (University of Maribor) </t>
+  </si>
+  <si>
+    <t>NAPCORE Task 4.4</t>
+  </si>
+  <si>
+    <t>Published Controlled Vocabulary</t>
   </si>
 </sst>
 </file>
@@ -465,7 +465,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -485,9 +484,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -504,10 +504,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -797,11 +793,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.7109375" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="2" max="2" width="46.28515625" customWidth="1"/>
     <col min="3" max="3" width="77.140625" customWidth="1"/>
     <col min="4" max="4" width="45.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="67.85546875" style="1" customWidth="1"/>
@@ -813,7 +809,7 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -855,7 +851,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -864,7 +860,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -872,11 +868,11 @@
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>102</v>
+      <c r="A8" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="C8" s="1"/>
     </row>
@@ -885,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C9" s="1"/>
     </row>
@@ -893,507 +889,495 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="B10" s="21" t="s">
+        <v>14</v>
+      </c>
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="B11" t="str">
+        <f>_xlfn.CONCAT(B1,"/",B10)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/1.2.0</v>
       </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>15</v>
+      <c r="A12" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="str">
-        <f>_xlfn.CONCAT(B1,"/",B12)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/1.2.0</v>
+        <v>18</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="B14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="2" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" t="s">
-        <v>101</v>
+        <v>38</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B22)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/c-its</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(B23)," ","-"),",",""),"ii","II"))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/datex-II</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B24)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/c-its</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/dino</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" t="s">
-        <v>101</v>
+        <v>43</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(B25)," ","-"),",",""),"ii","II"))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/datex-II</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" t="s">
-        <v>101</v>
+      <c r="A25" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B26)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/dino</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" t="s">
-        <v>101</v>
+      <c r="A26" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" t="s">
-        <v>101</v>
+        <v>53</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" t="s">
-        <v>101</v>
+      <c r="A28" t="str">
+        <f t="shared" ref="A28:A31" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B28)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gbfs</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" t="s">
-        <v>101</v>
+      <c r="A29" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gml</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <f t="shared" ref="A30:A33" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B30)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gbfs</v>
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gtfs</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" t="s">
-        <v>101</v>
+        <v>58</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gml</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gtfs-rt</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" t="s">
-        <v>101</v>
+        <v>60</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gtfs</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" t="s">
-        <v>101</v>
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gtfs-rt</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" t="s">
-        <v>101</v>
+      <c r="A33" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E34" t="s">
-        <v>101</v>
+      <c r="A34" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B34)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/netex</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E35" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="str">
+      <c r="A35" s="9" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B35)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocit-o</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B36)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/netex</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36" t="s">
-        <v>101</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocit-c</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="str">
+      <c r="A37" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B37)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocit-o</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B38)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocit-c</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="17" t="s">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocpi</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E38" t="s">
-        <v>101</v>
+      <c r="C37" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B39)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocpi</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" t="s">
-        <v>101</v>
+      <c r="A39" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E40" t="s">
-        <v>101</v>
+        <v>84</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E41" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E42" t="s">
-        <v>101</v>
+      <c r="A42" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B42)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/siri</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E43" t="s">
-        <v>101</v>
+      <c r="A43" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B43)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tn-its</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B44)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/siri</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" t="s">
-        <v>101</v>
+      <c r="A44" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B45)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tn-its</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tpegml</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E45" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E46" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B47)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tpegml</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="14" t="s">
+      <c r="A46" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B46)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/other</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E47" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B48)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/other</v>
-      </c>
-      <c r="B48" s="6" t="s">
+      <c r="C46" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E48" t="s">
-        <v>101</v>
+      <c r="E46" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:C47">
-    <sortCondition ref="B20:B47"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:C45">
+    <sortCondition ref="B18:B45"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B15" r:id="rId1" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
+    <hyperlink ref="B13" r:id="rId1" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1401,6 +1385,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1409,7 +1404,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006748505E66128D48AAED90CD5CD3616F" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b912ec8155dd4e933917767331a7e7b9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa" xmlns:ns3="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f994fb40b965d01e7e08c4f92ceb61cd" ns2:_="" ns3:_="">
     <xsd:import namespace="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
@@ -1610,18 +1605,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0610B8D-6EB9-4C25-8CE0-612AE3B494D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
+    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1629,7 +1624,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0C5E93-65BA-4187-9929-805FF0E80B6F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1646,15 +1641,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0610B8D-6EB9-4C25-8CE0-612AE3B494D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
-    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>